--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487900_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487900_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5773</v>
+        <v>1.9035</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7044</v>
+        <v>3.4122</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.127</v>
+        <v>-1.5087</v>
       </c>
       <c r="G2" t="n">
         <v>-2.5635</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3083</v>
+        <v>0.6345</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1771</v>
+        <v>0.8849</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1312</v>
+        <v>-0.2504</v>
       </c>
       <c r="V2" t="n">
         <v>1.7513</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2575</v>
+        <v>1.6228</v>
       </c>
       <c r="E3" t="n">
-        <v>0.315</v>
+        <v>5.3197</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9425</v>
+        <v>-3.6969</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9340000000000001</v>
+        <v>-3.1822</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5886</v>
+        <v>0.4027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3454</v>
+        <v>-3.5849</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1385</v>
+        <v>-0.5081</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5115</v>
+        <v>0.803</v>
       </c>
       <c r="L3" t="n">
-        <v>0.627</v>
+        <v>-1.3112</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2045</v>
+        <v>-2.6741</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9228</v>
+        <v>-0.4004</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2817</v>
+        <v>-2.2737</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6649</v>
+        <v>2.2893</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4247</v>
+        <v>-0.99</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7829</v>
+        <v>-0.5967</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3583</v>
+        <v>-0.3933</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1238</v>
+        <v>4.5463</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>7.4651</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1238</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7091</v>
+        <v>1.0021</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6115</v>
+        <v>0.5293</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.9024</v>
+        <v>0.4728</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.1822</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4027</v>
+        <v>0.5886</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.5849</v>
+        <v>0.3454</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5081</v>
+        <v>2.1385</v>
       </c>
       <c r="K4" t="n">
-        <v>0.803</v>
+        <v>1.5115</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3112</v>
+        <v>0.627</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6741</v>
+        <v>-1.2045</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4004</v>
+        <v>-0.9228</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.2737</v>
+        <v>-0.2817</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2893</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9037</v>
+        <v>-0.6801</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3049</v>
+        <v>-0.5686</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5988</v>
+        <v>-0.1115</v>
       </c>
       <c r="V4" t="n">
-        <v>4.5463</v>
+        <v>0.1238</v>
       </c>
       <c r="W4" t="n">
-        <v>7.4651</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.9188</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. TSEGAKELE</t>
+          <t>S. FRANCO GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.541</v>
+        <v>-0.8602</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4987</v>
+        <v>-0.9946</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0423</v>
+        <v>0.1344</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6504</v>
+        <v>-2.7614</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2283</v>
+        <v>-0.1659</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4221</v>
+        <v>-2.5954</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7563</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7955</v>
+        <v>0.2303</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0392</v>
+        <v>-0.8891</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.894</v>
+        <v>-2.1025</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4328</v>
+        <v>-0.3962</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4613</v>
+        <v>-1.7063</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8325</v>
+        <v>2.0812</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8325</v>
+        <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5069</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2577</v>
+        <v>-0.3357</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2492</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.23</v>
+        <v>0.7076</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.23</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. FRANCO GARCIA</t>
+          <t>A. TSEGAKELE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9435</v>
+        <v>-0.9314</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6375</v>
+        <v>-0.713</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.306</v>
+        <v>-0.2184</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.7614</v>
+        <v>-1.6504</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1659</v>
+        <v>-1.2283</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.5954</v>
+        <v>-0.4221</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6588000000000001</v>
+        <v>-0.7563</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2303</v>
+        <v>-0.7955</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8891</v>
+        <v>0.0392</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1025</v>
+        <v>-0.894</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3962</v>
+        <v>-0.4328</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7063</v>
+        <v>-0.4613</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0812</v>
+        <v>0.8325</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0812</v>
+        <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9709</v>
+        <v>0.1164</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9786</v>
+        <v>0.0434</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9923</v>
+        <v>0.0731</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7076</v>
+        <v>-0.23</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7076</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1985</v>
+        <v>-2.1729</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.2733</v>
+        <v>-3.1009</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0748</v>
+        <v>0.928</v>
       </c>
       <c r="G7" t="n">
         <v>-2.2174</v>
@@ -1000,13 +1000,13 @@
         <v>2.7055</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7594</v>
+        <v>-0.7338</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.721</v>
+        <v>-0.5486</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0384</v>
+        <v>-0.1852</v>
       </c>
       <c r="V7" t="n">
         <v>4.3163</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>I. DUKE TOUSSAINT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.4377</v>
+        <v>-4.0551</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-3.6414</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.6206</v>
+        <v>-0.4137</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1528</v>
+        <v>-1.717</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2367</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3896</v>
+        <v>-1.1691</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0311</v>
+        <v>-0.3534</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9594</v>
+        <v>0.3218</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9283</v>
+        <v>-0.6752</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1839</v>
+        <v>-1.3636</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7227</v>
+        <v>-0.8697</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4613</v>
+        <v>-0.4939</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2081</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1579</v>
+        <v>-0.695</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1924</v>
+        <v>-0.3962</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3503</v>
+        <v>-0.2988</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.9188</v>
+        <v>0.23</v>
       </c>
       <c r="W8" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-2.9188</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. DUKE TOUSSAINT</t>
+          <t>G. ARCOS GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4711</v>
+        <v>-4.1886</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.0281</v>
+        <v>-1.9038</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.443</v>
+        <v>-2.2848</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.717</v>
+        <v>-2.4052</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5479000000000001</v>
+        <v>0.4947</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1691</v>
+        <v>-2.8999</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3534</v>
+        <v>0.1341</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3218</v>
+        <v>0.9358</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6752</v>
+        <v>-0.8017</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3636</v>
+        <v>-2.5393</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8697</v>
+        <v>-0.4411</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4939</v>
+        <v>-2.0982</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8731</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.111</v>
+        <v>-0.4078</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7829</v>
+        <v>-0.1866</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3281</v>
+        <v>-0.2211</v>
       </c>
       <c r="V9" t="n">
-        <v>0.23</v>
+        <v>-1.1675</v>
       </c>
       <c r="W9" t="n">
         <v>0.23</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. ARCOS GONZALEZ</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4928</v>
+        <v>-4.5345</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8263</v>
+        <v>-1.0314</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6665</v>
+        <v>-3.5032</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4052</v>
+        <v>-1.1528</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4947</v>
+        <v>0.2367</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8999</v>
+        <v>-1.3896</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1341</v>
+        <v>0.0311</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9358</v>
+        <v>0.9594</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8017</v>
+        <v>-0.9283</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5393</v>
+        <v>-1.1839</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4411</v>
+        <v>-0.7227</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0982</v>
+        <v>-0.4613</v>
       </c>
       <c r="P10" t="n">
         <v>-0.2081</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7119</v>
+        <v>-0.2548</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1091</v>
+        <v>-0.0219</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6028</v>
+        <v>-0.2329</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1675</v>
+        <v>-2.9188</v>
       </c>
       <c r="W10" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3975</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.5407</v>
+        <v>-12.2143</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.449999999999999</v>
+        <v>-2.123899999999999</v>
       </c>
       <c r="F11" t="n">
         <v>-10.0905</v>
@@ -1312,16 +1312,16 @@
         <v>15.6089</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.224299999999999</v>
+        <v>-3.8982</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.0522</v>
+        <v>-1.726</v>
       </c>
       <c r="U11" t="n">
         <v>-2.172</v>
       </c>
       <c r="V11" t="n">
-        <v>7.358999999999998</v>
+        <v>7.358999999999999</v>
       </c>
       <c r="W11" t="n">
         <v>14.5765</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.1199</v>
+        <v>7.9009</v>
       </c>
       <c r="E12" t="n">
-        <v>7.0463</v>
+        <v>7.4749</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0737</v>
+        <v>0.426</v>
       </c>
       <c r="G12" t="n">
         <v>7.5065</v>
@@ -1390,13 +1390,13 @@
         <v>1.0406</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1972</v>
+        <v>-0.4162</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.64</v>
+        <v>-0.2114</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5571</v>
+        <v>-0.2048</v>
       </c>
       <c r="V12" t="n">
         <v>-0.23</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.281</v>
+        <v>5.6953</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2595</v>
+        <v>2.938</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0215</v>
+        <v>2.7573</v>
       </c>
       <c r="G13" t="n">
         <v>4.6619</v>
@@ -1468,13 +1468,13 @@
         <v>1.8731</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2435</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6458</v>
+        <v>0.3244</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5977</v>
+        <v>0.3334</v>
       </c>
       <c r="V13" t="n">
         <v>0.5838</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>P. SANCHEZ INFANTES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4949</v>
+        <v>3.5371</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0877</v>
+        <v>1.4571</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4072</v>
+        <v>2.08</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8945</v>
+        <v>4.0977</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2837</v>
+        <v>1.4925</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1782</v>
+        <v>2.6052</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6784</v>
+        <v>4.2327</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3202</v>
+        <v>2.7011</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9986</v>
+        <v>1.5316</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2162</v>
+        <v>-0.135</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0366</v>
+        <v>-1.2086</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1796</v>
+        <v>1.0736</v>
       </c>
       <c r="P14" t="n">
+        <v>-1.2487</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-3.1218</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.8731</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.4581</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1162</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X14" t="n">
         <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-1.0406</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.0406</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.2466</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2824</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.0358</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.3538</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.1675</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.8137</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. SANCHEZ INFANTES</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2204</v>
+        <v>2.9183</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4927</v>
+        <v>2.7126</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7277</v>
+        <v>0.2057</v>
       </c>
       <c r="G15" t="n">
-        <v>4.0977</v>
+        <v>0.9416</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4925</v>
+        <v>0.5889</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6052</v>
+        <v>0.3527</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2327</v>
+        <v>1.2317</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7011</v>
+        <v>1.1321</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5316</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.135</v>
+        <v>-0.2901</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2086</v>
+        <v>-0.5432</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0736</v>
+        <v>0.2531</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.2487</v>
+        <v>2.7055</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8731</v>
+        <v>2.7055</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8586</v>
+        <v>0.4387</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8482</v>
+        <v>0.3134</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0104</v>
+        <v>0.1253</v>
       </c>
       <c r="V15" t="n">
-        <v>0.23</v>
+        <v>-1.1675</v>
       </c>
       <c r="W15" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9936</v>
+        <v>2.2219</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6411</v>
+        <v>1.8734</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3525</v>
+        <v>0.3485</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9416</v>
+        <v>1.8945</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5889</v>
+        <v>-0.2837</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3527</v>
+        <v>2.1782</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2317</v>
+        <v>1.6784</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1321</v>
+        <v>-0.3202</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09959999999999999</v>
+        <v>1.9986</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2901</v>
+        <v>0.2162</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5432</v>
+        <v>0.0366</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2531</v>
+        <v>0.1796</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7055</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7055</v>
+        <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.486</v>
+        <v>-0.0264</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7581</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2721</v>
+        <v>-0.0946</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1675</v>
+        <v>0.3538</v>
       </c>
       <c r="W16" t="n">
         <v>1.1675</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3351</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0394</v>
+        <v>-0.2352</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7745</v>
+        <v>1.8817</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7351</v>
+        <v>-2.1168</v>
       </c>
       <c r="G17" t="n">
         <v>0.5726</v>
@@ -1780,13 +1780,13 @@
         <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0099</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0438</v>
+        <v>0.0634</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0537</v>
+        <v>0.672</v>
       </c>
       <c r="V17" t="n">
         <v>-1.7513</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>J. BLACK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.717</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5173</v>
+        <v>-1.0978</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0376</v>
+        <v>0.3808</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2503</v>
+        <v>0.0441</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9319</v>
+        <v>-1.143</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1822</v>
+        <v>1.1871</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0548</v>
+        <v>-0.2211</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2318</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.823</v>
+        <v>0.5788</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8045</v>
+        <v>0.2652</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1637</v>
+        <v>-0.3431</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3592</v>
+        <v>0.6082</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q18" t="n">
         <v>-3.1218</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>1.173</v>
+        <v>0.4877</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3197</v>
+        <v>0.2639</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1468</v>
+        <v>0.2238</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9376</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.23</v>
+        <v>1.9813</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1675</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6747</v>
+        <v>-1.0637</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6187</v>
+        <v>0.083</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2934</v>
+        <v>-1.1466</v>
       </c>
       <c r="G19" t="n">
         <v>0.6837</v>
@@ -1936,13 +1936,13 @@
         <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0204</v>
+        <v>0.6314</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1678</v>
+        <v>0.632</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1474</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>-2.795</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0149</v>
+        <v>-1.3622</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2242</v>
+        <v>-1.5889</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2093</v>
+        <v>0.2266</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.172</v>
+        <v>0.2503</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1024</v>
+        <v>-0.9319</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2744</v>
+        <v>1.1822</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.678</v>
+        <v>1.0548</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6332</v>
+        <v>0.2318</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3112</v>
+        <v>0.823</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.494</v>
+        <v>-0.8045</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5308</v>
+        <v>-1.1637</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0367</v>
+        <v>0.3592</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6244</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4162</v>
+        <v>2.0812</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2591</v>
+        <v>0.3657</v>
       </c>
       <c r="T20" t="n">
-        <v>0.972</v>
+        <v>0.2482</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2871</v>
+        <v>0.1175</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4776</v>
+        <v>-0.9376</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.4776</v>
+        <v>0.23</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BLACK</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3599</v>
+        <v>-1.8237</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7407</v>
+        <v>-1.9742</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3808</v>
+        <v>0.1505</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0441</v>
+        <v>-1.172</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.143</v>
+        <v>0.1024</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1871</v>
+        <v>-1.2744</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2211</v>
+        <v>-0.678</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7999000000000001</v>
+        <v>0.6332</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5788</v>
+        <v>-1.3112</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2652</v>
+        <v>-0.494</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3431</v>
+        <v>-0.5308</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6082</v>
+        <v>0.0367</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.2487</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8731</v>
+        <v>0.4162</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1553</v>
+        <v>0.4503</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3791</v>
+        <v>0.222</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2238</v>
+        <v>0.2284</v>
       </c>
       <c r="V21" t="n">
+        <v>-0.4776</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.4776</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.9813</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-1.9813</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0042</v>
+        <v>-4.5312</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3479</v>
+        <v>-3.6694</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6563</v>
+        <v>-0.8618</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7649</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9688</v>
+        <v>0.4418</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4534</v>
+        <v>0.1319</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5154</v>
+        <v>0.3099</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1675</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>12.5406</v>
+        <v>12.5405</v>
       </c>
       <c r="E23" t="n">
         <v>10.0904</v>
       </c>
       <c r="F23" t="n">
-        <v>2.450299999999999</v>
+        <v>2.4502</v>
       </c>
       <c r="G23" t="n">
         <v>16.716</v>
@@ -2224,19 +2224,19 @@
         <v>16.31</v>
       </c>
       <c r="K23" t="n">
-        <v>4.4108</v>
+        <v>4.410800000000001</v>
       </c>
       <c r="L23" t="n">
         <v>11.8993</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4061999999999999</v>
+        <v>0.4062000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>-5.8602</v>
       </c>
       <c r="O23" t="n">
-        <v>6.266</v>
+        <v>6.266000000000001</v>
       </c>
       <c r="P23" t="n">
         <v>-1.0407</v>
@@ -2248,13 +2248,13 @@
         <v>14.5683</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2242</v>
+        <v>4.224299999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1719</v>
+        <v>2.1721</v>
       </c>
       <c r="U23" t="n">
-        <v>2.0523</v>
+        <v>2.0522</v>
       </c>
       <c r="V23" t="n">
         <v>-7.3589</v>
